--- a/human_resources_forms/004_organizational_culture_survey--human_resources_forms.xlsx
+++ b/human_resources_forms/004_organizational_culture_survey--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>employee_survey</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Employee Survey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please answer the questions honestly to provide valuable feedback for the company's improvement</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>management_survey</t>
+          <t>company_values</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Management Survey</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What are the company's core values?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Think about the most important principles that guide the company's behavior</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,41 +574,49 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>organizational_survey</t>
+          <t>communication_style</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Organizational Culture</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How would you rate the company's communication style?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Consider how well the company shares information with employees</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>leadership_survey</t>
+          <t>decision_making</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Leadership Survey</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What do you think is the most significant factor in the company's decision-making process?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Consider the role of employee feedback and involvement</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>employee_survey_2</t>
+          <t>leadership_style</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Employee Survey</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>How would you rate the company's leadership style?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Consider how leaders motivate and support employees</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>management_survey_2</t>
+          <t>company_culture</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Management Survey</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How do you rate the overall culture of the company?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Consider how well the company promotes a positive work environment</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>organizational_survey_2</t>
+          <t>policy_changes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Organizational Culture</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What changes would you like to see in the company's current policies?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Be honest and provide specific examples</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>leadership_survey_2</t>
+          <t>manager_support</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Leadership Survey</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>How would you rate the level of support from your manager?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Consider how well your manager listens to your concerns</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>employee_survey_3</t>
+          <t>sick_leave</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Employee Survey</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>How many days do you take sick leave per year?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Only include days actually taken, not expected or available</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>management_survey_3</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Management Survey</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is your role in the company?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Provide your job title and department</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>organizational_survey_3</t>
+          <t>years_with_company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Organizational Culture</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>How many years have you been with the company?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Only include years actually working at the company</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>leadership_survey_3</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Leadership Survey</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What department do you belong to?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Provide your department name</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -791,322 +839,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>employee_survey_4</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Employee Survey</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please submit your answers</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>management_survey_4</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Management Survey</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>organizational_survey_4</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Organizational Culture</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>leadership_survey_4</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Leadership Survey</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>employee_survey_5</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Employee Survey</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>management_survey_5</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Management Survey</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>organizational_survey_5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Organizational Culture</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>leadership_survey_5</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Leadership Survey</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>employee_survey_6</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Employee Survey</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>management_survey_6</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Management Survey</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>organizational_survey_6</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Organizational Culture</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>leadership_survey_6</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Leadership Survey</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Form ID</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1121,12 +874,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1149,34 +902,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>submit_choices</t>
+          <t>decision_making_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>employee_input_is_always_considered</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Employee input is always considered</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>decision_making_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>employee_input_is_sometimes_considered</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Employee input is sometimes considered</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decision_making_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>employee_input_is_rarely_considered</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Employee input is rarely considered</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>decision_making_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>employee_input_is_never_considered</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Employee input is never considered</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>submit_choices</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>submit_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
